--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="296">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -601,6 +601,15 @@
     <t>['65', '90+1']</t>
   </si>
   <si>
+    <t>['41', '60']</t>
+  </si>
+  <si>
+    <t>['23', '37']</t>
+  </si>
+  <si>
+    <t>['10', '90']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -887,6 +896,12 @@
   </si>
   <si>
     <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['69', '72']</t>
+  </si>
+  <si>
+    <t>['35']</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP154"/>
+  <dimension ref="A1:BP160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1504,7 +1519,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1710,7 +1725,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2122,7 +2137,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2534,7 +2549,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2740,7 +2755,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2946,7 +2961,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3152,7 +3167,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3436,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ11">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3564,7 +3579,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3642,10 +3657,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3851,7 +3866,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3976,7 +3991,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4057,7 +4072,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ14">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4388,7 +4403,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4466,7 +4481,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.67</v>
@@ -4594,7 +4609,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4675,7 +4690,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ17">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4800,7 +4815,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -4878,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18">
         <v>2.44</v>
@@ -5084,10 +5099,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5212,7 +5227,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5624,7 +5639,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -5702,7 +5717,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>1.56</v>
@@ -5830,7 +5845,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6448,7 +6463,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6654,7 +6669,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6860,7 +6875,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6941,7 +6956,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ28">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR28">
         <v>1.96</v>
@@ -7147,7 +7162,7 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR29">
         <v>1.99</v>
@@ -7272,7 +7287,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7350,10 +7365,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ30">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>0.79</v>
@@ -7478,7 +7493,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7556,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>1.13</v>
@@ -7765,7 +7780,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ32">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR32">
         <v>0.9399999999999999</v>
@@ -7890,7 +7905,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8096,7 +8111,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8174,7 +8189,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ34">
         <v>1.67</v>
@@ -8383,7 +8398,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ35">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR35">
         <v>1.49</v>
@@ -8508,7 +8523,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8589,7 +8604,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR36">
         <v>1.71</v>
@@ -8714,7 +8729,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -8792,7 +8807,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ37">
         <v>1.67</v>
@@ -8920,7 +8935,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -8998,7 +9013,7 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ38">
         <v>1.56</v>
@@ -9207,7 +9222,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ39">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR39">
         <v>1.65</v>
@@ -9332,7 +9347,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9538,7 +9553,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9744,7 +9759,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -9950,7 +9965,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10362,7 +10377,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10646,7 +10661,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.13</v>
@@ -10774,7 +10789,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -10855,7 +10870,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ47">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR47">
         <v>1.4</v>
@@ -10980,7 +10995,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11061,7 +11076,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
         <v>1.7</v>
@@ -11186,7 +11201,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11267,7 +11282,7 @@
         <v>1</v>
       </c>
       <c r="AQ49">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR49">
         <v>1.77</v>
@@ -11392,7 +11407,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11676,10 +11691,10 @@
         <v>2</v>
       </c>
       <c r="AP51">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ51">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.47</v>
@@ -11804,7 +11819,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -11882,7 +11897,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52">
         <v>1.38</v>
@@ -12010,7 +12025,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12091,7 +12106,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ53">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR53">
         <v>1.25</v>
@@ -12216,7 +12231,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12422,7 +12437,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12500,7 +12515,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ55">
         <v>1.13</v>
@@ -12628,7 +12643,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12834,7 +12849,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13040,7 +13055,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13118,7 +13133,7 @@
         <v>1.67</v>
       </c>
       <c r="AP58">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
         <v>1.56</v>
@@ -13324,7 +13339,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ59">
         <v>1.56</v>
@@ -13452,7 +13467,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13658,7 +13673,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -13736,10 +13751,10 @@
         <v>0.33</v>
       </c>
       <c r="AP61">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR61">
         <v>1.4</v>
@@ -14070,7 +14085,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14276,7 +14291,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14688,7 +14703,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -14769,7 +14784,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ66">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR66">
         <v>1.63</v>
@@ -14975,7 +14990,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ67">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR67">
         <v>2.27</v>
@@ -15306,7 +15321,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15512,7 +15527,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15718,7 +15733,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15799,7 +15814,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ71">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -16002,10 +16017,10 @@
         <v>0.33</v>
       </c>
       <c r="AP72">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ72">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -16130,7 +16145,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16417,7 +16432,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ74">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR74">
         <v>1.62</v>
@@ -16748,7 +16763,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16826,7 +16841,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>1.5</v>
@@ -16954,7 +16969,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17032,7 +17047,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ77">
         <v>2.13</v>
@@ -17241,7 +17256,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ78">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR78">
         <v>1.65</v>
@@ -17444,7 +17459,7 @@
         <v>1.5</v>
       </c>
       <c r="AP79">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ79">
         <v>1.56</v>
@@ -17778,7 +17793,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17984,7 +17999,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18062,7 +18077,7 @@
         <v>3</v>
       </c>
       <c r="AP82">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
         <v>2.44</v>
@@ -18190,7 +18205,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18396,7 +18411,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18602,7 +18617,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18808,7 +18823,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -18889,7 +18904,7 @@
         <v>1</v>
       </c>
       <c r="AQ86">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.49</v>
@@ -19014,7 +19029,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19220,7 +19235,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19426,7 +19441,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19507,7 +19522,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ89">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR89">
         <v>1.42</v>
@@ -19632,7 +19647,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19713,7 +19728,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ90">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR90">
         <v>1.7</v>
@@ -19916,7 +19931,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ91">
         <v>1.13</v>
@@ -20122,7 +20137,7 @@
         <v>3</v>
       </c>
       <c r="AP92">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ92">
         <v>2.13</v>
@@ -20331,7 +20346,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR93">
         <v>1.52</v>
@@ -20534,7 +20549,7 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ94">
         <v>1.5</v>
@@ -20662,7 +20677,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20743,7 +20758,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ95">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR95">
         <v>1.41</v>
@@ -21074,7 +21089,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21155,7 +21170,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ97">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR97">
         <v>1.4</v>
@@ -21280,7 +21295,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21358,7 +21373,7 @@
         <v>2.4</v>
       </c>
       <c r="AP98">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ98">
         <v>2.44</v>
@@ -21692,7 +21707,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q100">
         <v>1.95</v>
@@ -21770,7 +21785,7 @@
         <v>1.4</v>
       </c>
       <c r="AP100">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>0.89</v>
@@ -21898,7 +21913,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -21976,7 +21991,7 @@
         <v>1.4</v>
       </c>
       <c r="AP101">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ101">
         <v>1.38</v>
@@ -22391,7 +22406,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ103">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR103">
         <v>1.96</v>
@@ -22516,7 +22531,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22803,7 +22818,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ105">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR105">
         <v>1.68</v>
@@ -22928,7 +22943,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23134,7 +23149,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23546,7 +23561,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23627,7 +23642,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ109">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR109">
         <v>1.49</v>
@@ -23752,7 +23767,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24036,10 +24051,10 @@
         <v>1.6</v>
       </c>
       <c r="AP111">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ111">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR111">
         <v>1.23</v>
@@ -24164,7 +24179,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24370,7 +24385,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24451,7 +24466,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ113">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR113">
         <v>1.37</v>
@@ -24576,7 +24591,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24782,7 +24797,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -24863,7 +24878,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ115">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
         <v>1.64</v>
@@ -24988,7 +25003,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25066,10 +25081,10 @@
         <v>0.83</v>
       </c>
       <c r="AP116">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR116">
         <v>1.56</v>
@@ -25194,7 +25209,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25272,7 +25287,7 @@
         <v>0.33</v>
       </c>
       <c r="AP117">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ117">
         <v>0.22</v>
@@ -25400,7 +25415,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25478,7 +25493,7 @@
         <v>2.17</v>
       </c>
       <c r="AP118">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ118">
         <v>2.44</v>
@@ -25606,7 +25621,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25812,7 +25827,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26018,7 +26033,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26099,7 +26114,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ121">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR121">
         <v>1.92</v>
@@ -26224,7 +26239,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26508,7 +26523,7 @@
         <v>0</v>
       </c>
       <c r="AP123">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ123">
         <v>0.13</v>
@@ -26842,7 +26857,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27048,7 +27063,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27335,7 +27350,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ127">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR127">
         <v>1.54</v>
@@ -27666,7 +27681,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27747,7 +27762,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ129">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR129">
         <v>1.5</v>
@@ -27872,7 +27887,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27950,7 +27965,7 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ130">
         <v>1.67</v>
@@ -28078,7 +28093,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q131">
         <v>3.3</v>
@@ -28284,7 +28299,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28365,7 +28380,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ132">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR132">
         <v>1.64</v>
@@ -28490,7 +28505,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28568,7 +28583,7 @@
         <v>2.29</v>
       </c>
       <c r="AP133">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ133">
         <v>2.44</v>
@@ -28696,7 +28711,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -28774,10 +28789,10 @@
         <v>1.67</v>
       </c>
       <c r="AP134">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR134">
         <v>1.67</v>
@@ -29108,7 +29123,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29186,10 +29201,10 @@
         <v>1.83</v>
       </c>
       <c r="AP136">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ136">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR136">
         <v>1.21</v>
@@ -29314,7 +29329,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29520,7 +29535,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29932,7 +29947,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30344,7 +30359,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30837,7 +30852,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ144">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR144">
         <v>1.49</v>
@@ -30962,7 +30977,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31040,7 +31055,7 @@
         <v>1.29</v>
       </c>
       <c r="AP145">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AQ145">
         <v>1.5</v>
@@ -31168,7 +31183,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31249,7 +31264,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ146">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR146">
         <v>1.51</v>
@@ -31374,7 +31389,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31658,10 +31673,10 @@
         <v>1.29</v>
       </c>
       <c r="AP148">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ148">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR148">
         <v>1.74</v>
@@ -31864,10 +31879,10 @@
         <v>0.88</v>
       </c>
       <c r="AP149">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ149">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR149">
         <v>1.2</v>
@@ -31992,7 +32007,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32404,7 +32419,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32482,10 +32497,10 @@
         <v>1.57</v>
       </c>
       <c r="AP152">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ152">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR152">
         <v>1.2</v>
@@ -32816,7 +32831,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -32894,10 +32909,10 @@
         <v>2</v>
       </c>
       <c r="AP154">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ154">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AR154">
         <v>1.69</v>
@@ -32973,6 +32988,1242 @@
       </c>
       <c r="BP154">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7491643</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45674.60416666666</v>
+      </c>
+      <c r="F155">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>83</v>
+      </c>
+      <c r="H155" t="s">
+        <v>76</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>2</v>
+      </c>
+      <c r="M155">
+        <v>2</v>
+      </c>
+      <c r="N155">
+        <v>4</v>
+      </c>
+      <c r="O155" t="s">
+        <v>195</v>
+      </c>
+      <c r="P155" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q155">
+        <v>2.88</v>
+      </c>
+      <c r="R155">
+        <v>2.38</v>
+      </c>
+      <c r="S155">
+        <v>3.25</v>
+      </c>
+      <c r="T155">
+        <v>1.29</v>
+      </c>
+      <c r="U155">
+        <v>3.5</v>
+      </c>
+      <c r="V155">
+        <v>2.38</v>
+      </c>
+      <c r="W155">
+        <v>1.53</v>
+      </c>
+      <c r="X155">
+        <v>5.5</v>
+      </c>
+      <c r="Y155">
+        <v>1.14</v>
+      </c>
+      <c r="Z155">
+        <v>2.31</v>
+      </c>
+      <c r="AA155">
+        <v>3.6</v>
+      </c>
+      <c r="AB155">
+        <v>2.8</v>
+      </c>
+      <c r="AC155">
+        <v>1.04</v>
+      </c>
+      <c r="AD155">
+        <v>10</v>
+      </c>
+      <c r="AE155">
+        <v>1.18</v>
+      </c>
+      <c r="AF155">
+        <v>4.5</v>
+      </c>
+      <c r="AG155">
+        <v>1.6</v>
+      </c>
+      <c r="AH155">
+        <v>2.2</v>
+      </c>
+      <c r="AI155">
+        <v>1.5</v>
+      </c>
+      <c r="AJ155">
+        <v>2.5</v>
+      </c>
+      <c r="AK155">
+        <v>1.43</v>
+      </c>
+      <c r="AL155">
+        <v>1.27</v>
+      </c>
+      <c r="AM155">
+        <v>1.57</v>
+      </c>
+      <c r="AN155">
+        <v>1</v>
+      </c>
+      <c r="AO155">
+        <v>1.38</v>
+      </c>
+      <c r="AP155">
+        <v>1</v>
+      </c>
+      <c r="AQ155">
+        <v>1.33</v>
+      </c>
+      <c r="AR155">
+        <v>1.57</v>
+      </c>
+      <c r="AS155">
+        <v>1.79</v>
+      </c>
+      <c r="AT155">
+        <v>3.36</v>
+      </c>
+      <c r="AU155">
+        <v>7</v>
+      </c>
+      <c r="AV155">
+        <v>6</v>
+      </c>
+      <c r="AW155">
+        <v>9</v>
+      </c>
+      <c r="AX155">
+        <v>9</v>
+      </c>
+      <c r="AY155">
+        <v>20</v>
+      </c>
+      <c r="AZ155">
+        <v>18</v>
+      </c>
+      <c r="BA155">
+        <v>7</v>
+      </c>
+      <c r="BB155">
+        <v>5</v>
+      </c>
+      <c r="BC155">
+        <v>12</v>
+      </c>
+      <c r="BD155">
+        <v>1.86</v>
+      </c>
+      <c r="BE155">
+        <v>6.25</v>
+      </c>
+      <c r="BF155">
+        <v>2.17</v>
+      </c>
+      <c r="BG155">
+        <v>1.33</v>
+      </c>
+      <c r="BH155">
+        <v>2.95</v>
+      </c>
+      <c r="BI155">
+        <v>1.57</v>
+      </c>
+      <c r="BJ155">
+        <v>2.23</v>
+      </c>
+      <c r="BK155">
+        <v>1.92</v>
+      </c>
+      <c r="BL155">
+        <v>1.77</v>
+      </c>
+      <c r="BM155">
+        <v>2.4</v>
+      </c>
+      <c r="BN155">
+        <v>1.49</v>
+      </c>
+      <c r="BO155">
+        <v>3.1</v>
+      </c>
+      <c r="BP155">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7491651</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45674.60416666666</v>
+      </c>
+      <c r="F156">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>79</v>
+      </c>
+      <c r="H156" t="s">
+        <v>72</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>1</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>1</v>
+      </c>
+      <c r="O156" t="s">
+        <v>92</v>
+      </c>
+      <c r="P156" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q156">
+        <v>4.5</v>
+      </c>
+      <c r="R156">
+        <v>2.2</v>
+      </c>
+      <c r="S156">
+        <v>2.5</v>
+      </c>
+      <c r="T156">
+        <v>1.4</v>
+      </c>
+      <c r="U156">
+        <v>2.75</v>
+      </c>
+      <c r="V156">
+        <v>2.75</v>
+      </c>
+      <c r="W156">
+        <v>1.4</v>
+      </c>
+      <c r="X156">
+        <v>8</v>
+      </c>
+      <c r="Y156">
+        <v>1.08</v>
+      </c>
+      <c r="Z156">
+        <v>3.85</v>
+      </c>
+      <c r="AA156">
+        <v>3.75</v>
+      </c>
+      <c r="AB156">
+        <v>1.84</v>
+      </c>
+      <c r="AC156">
+        <v>1.04</v>
+      </c>
+      <c r="AD156">
+        <v>10</v>
+      </c>
+      <c r="AE156">
+        <v>1.28</v>
+      </c>
+      <c r="AF156">
+        <v>3.4</v>
+      </c>
+      <c r="AG156">
+        <v>1.93</v>
+      </c>
+      <c r="AH156">
+        <v>1.93</v>
+      </c>
+      <c r="AI156">
+        <v>1.83</v>
+      </c>
+      <c r="AJ156">
+        <v>1.83</v>
+      </c>
+      <c r="AK156">
+        <v>1.93</v>
+      </c>
+      <c r="AL156">
+        <v>1.26</v>
+      </c>
+      <c r="AM156">
+        <v>1.23</v>
+      </c>
+      <c r="AN156">
+        <v>1.11</v>
+      </c>
+      <c r="AO156">
+        <v>0.63</v>
+      </c>
+      <c r="AP156">
+        <v>1</v>
+      </c>
+      <c r="AQ156">
+        <v>0.89</v>
+      </c>
+      <c r="AR156">
+        <v>1.25</v>
+      </c>
+      <c r="AS156">
+        <v>1.18</v>
+      </c>
+      <c r="AT156">
+        <v>2.43</v>
+      </c>
+      <c r="AU156">
+        <v>2</v>
+      </c>
+      <c r="AV156">
+        <v>6</v>
+      </c>
+      <c r="AW156">
+        <v>8</v>
+      </c>
+      <c r="AX156">
+        <v>7</v>
+      </c>
+      <c r="AY156">
+        <v>12</v>
+      </c>
+      <c r="AZ156">
+        <v>16</v>
+      </c>
+      <c r="BA156">
+        <v>4</v>
+      </c>
+      <c r="BB156">
+        <v>8</v>
+      </c>
+      <c r="BC156">
+        <v>12</v>
+      </c>
+      <c r="BD156">
+        <v>2.65</v>
+      </c>
+      <c r="BE156">
+        <v>7</v>
+      </c>
+      <c r="BF156">
+        <v>1.56</v>
+      </c>
+      <c r="BG156">
+        <v>1.24</v>
+      </c>
+      <c r="BH156">
+        <v>3.55</v>
+      </c>
+      <c r="BI156">
+        <v>1.42</v>
+      </c>
+      <c r="BJ156">
+        <v>2.63</v>
+      </c>
+      <c r="BK156">
+        <v>1.68</v>
+      </c>
+      <c r="BL156">
+        <v>2.04</v>
+      </c>
+      <c r="BM156">
+        <v>2.06</v>
+      </c>
+      <c r="BN156">
+        <v>1.66</v>
+      </c>
+      <c r="BO156">
+        <v>2.63</v>
+      </c>
+      <c r="BP156">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7491648</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45675.375</v>
+      </c>
+      <c r="F157">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>80</v>
+      </c>
+      <c r="H157" t="s">
+        <v>78</v>
+      </c>
+      <c r="I157">
+        <v>2</v>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>3</v>
+      </c>
+      <c r="L157">
+        <v>2</v>
+      </c>
+      <c r="M157">
+        <v>1</v>
+      </c>
+      <c r="N157">
+        <v>3</v>
+      </c>
+      <c r="O157" t="s">
+        <v>196</v>
+      </c>
+      <c r="P157" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q157">
+        <v>2.5</v>
+      </c>
+      <c r="R157">
+        <v>2.25</v>
+      </c>
+      <c r="S157">
+        <v>4.33</v>
+      </c>
+      <c r="T157">
+        <v>1.36</v>
+      </c>
+      <c r="U157">
+        <v>3</v>
+      </c>
+      <c r="V157">
+        <v>2.63</v>
+      </c>
+      <c r="W157">
+        <v>1.44</v>
+      </c>
+      <c r="X157">
+        <v>7</v>
+      </c>
+      <c r="Y157">
+        <v>1.1</v>
+      </c>
+      <c r="Z157">
+        <v>1.94</v>
+      </c>
+      <c r="AA157">
+        <v>3.3</v>
+      </c>
+      <c r="AB157">
+        <v>3.54</v>
+      </c>
+      <c r="AC157">
+        <v>1.04</v>
+      </c>
+      <c r="AD157">
+        <v>10</v>
+      </c>
+      <c r="AE157">
+        <v>1.25</v>
+      </c>
+      <c r="AF157">
+        <v>3.75</v>
+      </c>
+      <c r="AG157">
+        <v>1.76</v>
+      </c>
+      <c r="AH157">
+        <v>1.99</v>
+      </c>
+      <c r="AI157">
+        <v>1.73</v>
+      </c>
+      <c r="AJ157">
+        <v>2</v>
+      </c>
+      <c r="AK157">
+        <v>1.26</v>
+      </c>
+      <c r="AL157">
+        <v>1.27</v>
+      </c>
+      <c r="AM157">
+        <v>1.83</v>
+      </c>
+      <c r="AN157">
+        <v>1.5</v>
+      </c>
+      <c r="AO157">
+        <v>0.89</v>
+      </c>
+      <c r="AP157">
+        <v>1.67</v>
+      </c>
+      <c r="AQ157">
+        <v>0.8</v>
+      </c>
+      <c r="AR157">
+        <v>1.65</v>
+      </c>
+      <c r="AS157">
+        <v>1.01</v>
+      </c>
+      <c r="AT157">
+        <v>2.66</v>
+      </c>
+      <c r="AU157">
+        <v>10</v>
+      </c>
+      <c r="AV157">
+        <v>9</v>
+      </c>
+      <c r="AW157">
+        <v>13</v>
+      </c>
+      <c r="AX157">
+        <v>6</v>
+      </c>
+      <c r="AY157">
+        <v>28</v>
+      </c>
+      <c r="AZ157">
+        <v>17</v>
+      </c>
+      <c r="BA157">
+        <v>7</v>
+      </c>
+      <c r="BB157">
+        <v>5</v>
+      </c>
+      <c r="BC157">
+        <v>12</v>
+      </c>
+      <c r="BD157">
+        <v>1.58</v>
+      </c>
+      <c r="BE157">
+        <v>6.75</v>
+      </c>
+      <c r="BF157">
+        <v>2.55</v>
+      </c>
+      <c r="BG157">
+        <v>1.23</v>
+      </c>
+      <c r="BH157">
+        <v>3.65</v>
+      </c>
+      <c r="BI157">
+        <v>1.41</v>
+      </c>
+      <c r="BJ157">
+        <v>2.65</v>
+      </c>
+      <c r="BK157">
+        <v>1.66</v>
+      </c>
+      <c r="BL157">
+        <v>2.06</v>
+      </c>
+      <c r="BM157">
+        <v>2.02</v>
+      </c>
+      <c r="BN157">
+        <v>1.68</v>
+      </c>
+      <c r="BO157">
+        <v>2.55</v>
+      </c>
+      <c r="BP157">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7491649</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45675.375</v>
+      </c>
+      <c r="F158">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>86</v>
+      </c>
+      <c r="H158" t="s">
+        <v>75</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="N158">
+        <v>0</v>
+      </c>
+      <c r="O158" t="s">
+        <v>92</v>
+      </c>
+      <c r="P158" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q158">
+        <v>3.5</v>
+      </c>
+      <c r="R158">
+        <v>2.38</v>
+      </c>
+      <c r="S158">
+        <v>2.75</v>
+      </c>
+      <c r="T158">
+        <v>1.3</v>
+      </c>
+      <c r="U158">
+        <v>3.4</v>
+      </c>
+      <c r="V158">
+        <v>2.5</v>
+      </c>
+      <c r="W158">
+        <v>1.5</v>
+      </c>
+      <c r="X158">
+        <v>6</v>
+      </c>
+      <c r="Y158">
+        <v>1.13</v>
+      </c>
+      <c r="Z158">
+        <v>2.81</v>
+      </c>
+      <c r="AA158">
+        <v>3.4</v>
+      </c>
+      <c r="AB158">
+        <v>2.08</v>
+      </c>
+      <c r="AC158">
+        <v>1.03</v>
+      </c>
+      <c r="AD158">
+        <v>11</v>
+      </c>
+      <c r="AE158">
+        <v>1.18</v>
+      </c>
+      <c r="AF158">
+        <v>4.5</v>
+      </c>
+      <c r="AG158">
+        <v>1.6</v>
+      </c>
+      <c r="AH158">
+        <v>2.25</v>
+      </c>
+      <c r="AI158">
+        <v>1.53</v>
+      </c>
+      <c r="AJ158">
+        <v>2.38</v>
+      </c>
+      <c r="AK158">
+        <v>1.66</v>
+      </c>
+      <c r="AL158">
+        <v>1.26</v>
+      </c>
+      <c r="AM158">
+        <v>1.37</v>
+      </c>
+      <c r="AN158">
+        <v>1.38</v>
+      </c>
+      <c r="AO158">
+        <v>1.33</v>
+      </c>
+      <c r="AP158">
+        <v>1.33</v>
+      </c>
+      <c r="AQ158">
+        <v>1.3</v>
+      </c>
+      <c r="AR158">
+        <v>1.3</v>
+      </c>
+      <c r="AS158">
+        <v>1.36</v>
+      </c>
+      <c r="AT158">
+        <v>2.66</v>
+      </c>
+      <c r="AU158">
+        <v>2</v>
+      </c>
+      <c r="AV158">
+        <v>3</v>
+      </c>
+      <c r="AW158">
+        <v>3</v>
+      </c>
+      <c r="AX158">
+        <v>14</v>
+      </c>
+      <c r="AY158">
+        <v>5</v>
+      </c>
+      <c r="AZ158">
+        <v>18</v>
+      </c>
+      <c r="BA158">
+        <v>0</v>
+      </c>
+      <c r="BB158">
+        <v>5</v>
+      </c>
+      <c r="BC158">
+        <v>5</v>
+      </c>
+      <c r="BD158">
+        <v>2.23</v>
+      </c>
+      <c r="BE158">
+        <v>6.75</v>
+      </c>
+      <c r="BF158">
+        <v>1.77</v>
+      </c>
+      <c r="BG158">
+        <v>1.33</v>
+      </c>
+      <c r="BH158">
+        <v>2.95</v>
+      </c>
+      <c r="BI158">
+        <v>1.56</v>
+      </c>
+      <c r="BJ158">
+        <v>2.23</v>
+      </c>
+      <c r="BK158">
+        <v>1.9</v>
+      </c>
+      <c r="BL158">
+        <v>1.78</v>
+      </c>
+      <c r="BM158">
+        <v>2.4</v>
+      </c>
+      <c r="BN158">
+        <v>1.49</v>
+      </c>
+      <c r="BO158">
+        <v>3.15</v>
+      </c>
+      <c r="BP158">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7491650</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45675.375</v>
+      </c>
+      <c r="F159">
+        <v>18</v>
+      </c>
+      <c r="G159" t="s">
+        <v>87</v>
+      </c>
+      <c r="H159" t="s">
+        <v>77</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>2</v>
+      </c>
+      <c r="L159">
+        <v>2</v>
+      </c>
+      <c r="M159">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>3</v>
+      </c>
+      <c r="O159" t="s">
+        <v>197</v>
+      </c>
+      <c r="P159" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q159">
+        <v>3</v>
+      </c>
+      <c r="R159">
+        <v>2.25</v>
+      </c>
+      <c r="S159">
+        <v>3.4</v>
+      </c>
+      <c r="T159">
+        <v>1.36</v>
+      </c>
+      <c r="U159">
+        <v>3</v>
+      </c>
+      <c r="V159">
+        <v>2.63</v>
+      </c>
+      <c r="W159">
+        <v>1.44</v>
+      </c>
+      <c r="X159">
+        <v>7</v>
+      </c>
+      <c r="Y159">
+        <v>1.1</v>
+      </c>
+      <c r="Z159">
+        <v>2.37</v>
+      </c>
+      <c r="AA159">
+        <v>3.33</v>
+      </c>
+      <c r="AB159">
+        <v>2.63</v>
+      </c>
+      <c r="AC159">
+        <v>1.05</v>
+      </c>
+      <c r="AD159">
+        <v>9.5</v>
+      </c>
+      <c r="AE159">
+        <v>1.22</v>
+      </c>
+      <c r="AF159">
+        <v>4</v>
+      </c>
+      <c r="AG159">
+        <v>1.74</v>
+      </c>
+      <c r="AH159">
+        <v>2.02</v>
+      </c>
+      <c r="AI159">
+        <v>1.62</v>
+      </c>
+      <c r="AJ159">
+        <v>2.2</v>
+      </c>
+      <c r="AK159">
+        <v>1.44</v>
+      </c>
+      <c r="AL159">
+        <v>1.28</v>
+      </c>
+      <c r="AM159">
+        <v>1.53</v>
+      </c>
+      <c r="AN159">
+        <v>0.78</v>
+      </c>
+      <c r="AO159">
+        <v>1.13</v>
+      </c>
+      <c r="AP159">
+        <v>1</v>
+      </c>
+      <c r="AQ159">
+        <v>1</v>
+      </c>
+      <c r="AR159">
+        <v>1.15</v>
+      </c>
+      <c r="AS159">
+        <v>1.24</v>
+      </c>
+      <c r="AT159">
+        <v>2.39</v>
+      </c>
+      <c r="AU159">
+        <v>5</v>
+      </c>
+      <c r="AV159">
+        <v>4</v>
+      </c>
+      <c r="AW159">
+        <v>13</v>
+      </c>
+      <c r="AX159">
+        <v>10</v>
+      </c>
+      <c r="AY159">
+        <v>20</v>
+      </c>
+      <c r="AZ159">
+        <v>15</v>
+      </c>
+      <c r="BA159">
+        <v>4</v>
+      </c>
+      <c r="BB159">
+        <v>3</v>
+      </c>
+      <c r="BC159">
+        <v>7</v>
+      </c>
+      <c r="BD159">
+        <v>1.95</v>
+      </c>
+      <c r="BE159">
+        <v>6.25</v>
+      </c>
+      <c r="BF159">
+        <v>2.07</v>
+      </c>
+      <c r="BG159">
+        <v>1.37</v>
+      </c>
+      <c r="BH159">
+        <v>2.8</v>
+      </c>
+      <c r="BI159">
+        <v>1.64</v>
+      </c>
+      <c r="BJ159">
+        <v>2.1</v>
+      </c>
+      <c r="BK159">
+        <v>2.02</v>
+      </c>
+      <c r="BL159">
+        <v>1.68</v>
+      </c>
+      <c r="BM159">
+        <v>2.55</v>
+      </c>
+      <c r="BN159">
+        <v>1.44</v>
+      </c>
+      <c r="BO159">
+        <v>3.4</v>
+      </c>
+      <c r="BP159">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7491644</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45675.69791666666</v>
+      </c>
+      <c r="F160">
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>84</v>
+      </c>
+      <c r="H160" t="s">
+        <v>70</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>1</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>1</v>
+      </c>
+      <c r="O160" t="s">
+        <v>88</v>
+      </c>
+      <c r="P160" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q160">
+        <v>3</v>
+      </c>
+      <c r="R160">
+        <v>2.38</v>
+      </c>
+      <c r="S160">
+        <v>3</v>
+      </c>
+      <c r="T160">
+        <v>1.29</v>
+      </c>
+      <c r="U160">
+        <v>3.5</v>
+      </c>
+      <c r="V160">
+        <v>2.38</v>
+      </c>
+      <c r="W160">
+        <v>1.53</v>
+      </c>
+      <c r="X160">
+        <v>5.5</v>
+      </c>
+      <c r="Y160">
+        <v>1.14</v>
+      </c>
+      <c r="Z160">
+        <v>2.55</v>
+      </c>
+      <c r="AA160">
+        <v>3.75</v>
+      </c>
+      <c r="AB160">
+        <v>2.55</v>
+      </c>
+      <c r="AC160">
+        <v>1.01</v>
+      </c>
+      <c r="AD160">
+        <v>13</v>
+      </c>
+      <c r="AE160">
+        <v>1.18</v>
+      </c>
+      <c r="AF160">
+        <v>4.75</v>
+      </c>
+      <c r="AG160">
+        <v>1.53</v>
+      </c>
+      <c r="AH160">
+        <v>2.4</v>
+      </c>
+      <c r="AI160">
+        <v>1.5</v>
+      </c>
+      <c r="AJ160">
+        <v>2.5</v>
+      </c>
+      <c r="AK160">
+        <v>1.52</v>
+      </c>
+      <c r="AL160">
+        <v>1.25</v>
+      </c>
+      <c r="AM160">
+        <v>1.5</v>
+      </c>
+      <c r="AN160">
+        <v>1.89</v>
+      </c>
+      <c r="AO160">
+        <v>2.13</v>
+      </c>
+      <c r="AP160">
+        <v>2</v>
+      </c>
+      <c r="AQ160">
+        <v>1.89</v>
+      </c>
+      <c r="AR160">
+        <v>1.75</v>
+      </c>
+      <c r="AS160">
+        <v>1.6</v>
+      </c>
+      <c r="AT160">
+        <v>3.35</v>
+      </c>
+      <c r="AU160">
+        <v>6</v>
+      </c>
+      <c r="AV160">
+        <v>3</v>
+      </c>
+      <c r="AW160">
+        <v>10</v>
+      </c>
+      <c r="AX160">
+        <v>5</v>
+      </c>
+      <c r="AY160">
+        <v>20</v>
+      </c>
+      <c r="AZ160">
+        <v>9</v>
+      </c>
+      <c r="BA160">
+        <v>6</v>
+      </c>
+      <c r="BB160">
+        <v>6</v>
+      </c>
+      <c r="BC160">
+        <v>12</v>
+      </c>
+      <c r="BD160">
+        <v>2</v>
+      </c>
+      <c r="BE160">
+        <v>6.75</v>
+      </c>
+      <c r="BF160">
+        <v>1.95</v>
+      </c>
+      <c r="BG160">
+        <v>1.16</v>
+      </c>
+      <c r="BH160">
+        <v>4.4</v>
+      </c>
+      <c r="BI160">
+        <v>1.29</v>
+      </c>
+      <c r="BJ160">
+        <v>3.2</v>
+      </c>
+      <c r="BK160">
+        <v>1.48</v>
+      </c>
+      <c r="BL160">
+        <v>2.45</v>
+      </c>
+      <c r="BM160">
+        <v>1.74</v>
+      </c>
+      <c r="BN160">
+        <v>1.96</v>
+      </c>
+      <c r="BO160">
+        <v>2.1</v>
+      </c>
+      <c r="BP160">
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="301">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -610,6 +610,12 @@
     <t>['10', '90']</t>
   </si>
   <si>
+    <t>['3', '36']</t>
+  </si>
+  <si>
+    <t>['36', '90+1']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -902,6 +908,15 @@
   </si>
   <si>
     <t>['35']</t>
+  </si>
+  <si>
+    <t>['16', '69']</t>
+  </si>
+  <si>
+    <t>['46', '70', '77', '82', '90+1']</t>
+  </si>
+  <si>
+    <t>['40']</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP160"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1519,7 +1534,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1725,7 +1740,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2137,7 +2152,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2549,7 +2564,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2755,7 +2770,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2961,7 +2976,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3167,7 +3182,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3579,7 +3594,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -3863,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ13">
         <v>1.3</v>
@@ -3991,7 +4006,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4069,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ14">
         <v>1.89</v>
@@ -4278,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="AQ15">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4403,7 +4418,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4484,7 +4499,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4609,7 +4624,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4687,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ17">
         <v>1.33</v>
@@ -4815,7 +4830,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -4896,7 +4911,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5227,7 +5242,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5639,7 +5654,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -5845,7 +5860,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6463,7 +6478,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6669,7 +6684,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6875,7 +6890,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -7287,7 +7302,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7493,7 +7508,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7777,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ32">
         <v>1.33</v>
@@ -7905,7 +7920,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -7983,10 +7998,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ33">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR33">
         <v>1.09</v>
@@ -8111,7 +8126,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8192,7 +8207,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ34">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR34">
         <v>1.8</v>
@@ -8395,7 +8410,7 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ35">
         <v>0.8</v>
@@ -8523,7 +8538,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8729,7 +8744,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -8810,7 +8825,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR37">
         <v>2.14</v>
@@ -8935,7 +8950,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9347,7 +9362,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9553,7 +9568,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9759,7 +9774,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -9965,7 +9980,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10046,7 +10061,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ43">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR43">
         <v>2.41</v>
@@ -10377,7 +10392,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10789,7 +10804,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -10867,7 +10882,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ47">
         <v>0.89</v>
@@ -10995,7 +11010,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11201,7 +11216,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11407,7 +11422,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11485,10 +11500,10 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ50">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR50">
         <v>0.97</v>
@@ -11819,7 +11834,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12025,7 +12040,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12103,7 +12118,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ53">
         <v>0.8</v>
@@ -12231,7 +12246,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12312,7 +12327,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ54">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR54">
         <v>1.87</v>
@@ -12437,7 +12452,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12643,7 +12658,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12849,7 +12864,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -13055,7 +13070,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13467,7 +13482,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13548,7 +13563,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ60">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR60">
         <v>1.59</v>
@@ -13673,7 +13688,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14085,7 +14100,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14291,7 +14306,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14372,7 +14387,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ64">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR64">
         <v>2.51</v>
@@ -14575,7 +14590,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ65">
         <v>0.13</v>
@@ -14703,7 +14718,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15193,7 +15208,7 @@
         <v>1.75</v>
       </c>
       <c r="AP68">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ68">
         <v>1.56</v>
@@ -15321,7 +15336,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15399,7 +15414,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ69">
         <v>1.13</v>
@@ -15527,7 +15542,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15608,7 +15623,7 @@
         <v>1</v>
       </c>
       <c r="AQ70">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR70">
         <v>1.66</v>
@@ -15733,7 +15748,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -16145,7 +16160,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16763,7 +16778,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16969,7 +16984,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17668,7 +17683,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ80">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
         <v>1.52</v>
@@ -17793,7 +17808,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17999,7 +18014,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18080,7 +18095,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR82">
         <v>1.62</v>
@@ -18205,7 +18220,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18411,7 +18426,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18489,7 +18504,7 @@
         <v>0</v>
       </c>
       <c r="AP84">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ84">
         <v>0.13</v>
@@ -18617,7 +18632,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18698,7 +18713,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ85">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR85">
         <v>1.57</v>
@@ -18823,7 +18838,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19029,7 +19044,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19107,7 +19122,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ87">
         <v>1.38</v>
@@ -19235,7 +19250,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19441,7 +19456,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19647,7 +19662,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -20677,7 +20692,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20964,7 +20979,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ96">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR96">
         <v>1.59</v>
@@ -21089,7 +21104,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21295,7 +21310,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21376,7 +21391,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ98">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR98">
         <v>1.68</v>
@@ -21579,7 +21594,7 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ99">
         <v>0.22</v>
@@ -21707,7 +21722,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q100">
         <v>1.95</v>
@@ -21913,7 +21928,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22197,7 +22212,7 @@
         <v>1.67</v>
       </c>
       <c r="AP102">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ102">
         <v>1.56</v>
@@ -22531,7 +22546,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22612,7 +22627,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ104">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR104">
         <v>1.47</v>
@@ -22943,7 +22958,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23149,7 +23164,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23561,7 +23576,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23639,7 +23654,7 @@
         <v>0.8</v>
       </c>
       <c r="AP109">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ109">
         <v>0.89</v>
@@ -23767,7 +23782,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23845,7 +23860,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ110">
         <v>0.89</v>
@@ -24179,7 +24194,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24260,7 +24275,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ112">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR112">
         <v>1.44</v>
@@ -24385,7 +24400,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24591,7 +24606,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24797,7 +24812,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25003,7 +25018,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25209,7 +25224,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25415,7 +25430,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25496,7 +25511,7 @@
         <v>1</v>
       </c>
       <c r="AQ118">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR118">
         <v>1.21</v>
@@ -25621,7 +25636,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25702,7 +25717,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ119">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR119">
         <v>1.77</v>
@@ -25827,7 +25842,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -26033,7 +26048,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26239,7 +26254,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26317,7 +26332,7 @@
         <v>1.43</v>
       </c>
       <c r="AP122">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ122">
         <v>1.56</v>
@@ -26857,7 +26872,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27063,7 +27078,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27141,7 +27156,7 @@
         <v>2.5</v>
       </c>
       <c r="AP126">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ126">
         <v>2.13</v>
@@ -27553,7 +27568,7 @@
         <v>1.14</v>
       </c>
       <c r="AP128">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ128">
         <v>0.89</v>
@@ -27681,7 +27696,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27759,7 +27774,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ129">
         <v>1.3</v>
@@ -27887,7 +27902,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -27968,7 +27983,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ130">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR130">
         <v>1.78</v>
@@ -28093,7 +28108,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q131">
         <v>3.3</v>
@@ -28174,7 +28189,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ131">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR131">
         <v>1.46</v>
@@ -28299,7 +28314,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28505,7 +28520,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28586,7 +28601,7 @@
         <v>1</v>
       </c>
       <c r="AQ133">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR133">
         <v>1.17</v>
@@ -28711,7 +28726,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29123,7 +29138,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29329,7 +29344,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29535,7 +29550,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29947,7 +29962,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30359,7 +30374,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30977,7 +30992,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31183,7 +31198,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31261,7 +31276,7 @@
         <v>1.13</v>
       </c>
       <c r="AP146">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ146">
         <v>1.3</v>
@@ -31389,7 +31404,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -31470,7 +31485,7 @@
         <v>1</v>
       </c>
       <c r="AQ147">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR147">
         <v>1.6</v>
@@ -32007,7 +32022,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32085,10 +32100,10 @@
         <v>1.5</v>
       </c>
       <c r="AP150">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ150">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AR150">
         <v>1.42</v>
@@ -32291,7 +32306,7 @@
         <v>0.25</v>
       </c>
       <c r="AP151">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ151">
         <v>0.22</v>
@@ -32419,7 +32434,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32706,7 +32721,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ153">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR153">
         <v>1.76</v>
@@ -32831,7 +32846,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33037,7 +33052,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33243,7 +33258,7 @@
         <v>92</v>
       </c>
       <c r="P156" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q156">
         <v>4.5</v>
@@ -34224,6 +34239,624 @@
       </c>
       <c r="BP160">
         <v>1.64</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7491645</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45676.39583333334</v>
+      </c>
+      <c r="F161">
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>85</v>
+      </c>
+      <c r="H161" t="s">
+        <v>73</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161">
+        <v>1</v>
+      </c>
+      <c r="L161">
+        <v>1</v>
+      </c>
+      <c r="M161">
+        <v>2</v>
+      </c>
+      <c r="N161">
+        <v>3</v>
+      </c>
+      <c r="O161" t="s">
+        <v>161</v>
+      </c>
+      <c r="P161" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q161">
+        <v>2.75</v>
+      </c>
+      <c r="R161">
+        <v>2.38</v>
+      </c>
+      <c r="S161">
+        <v>3.5</v>
+      </c>
+      <c r="T161">
+        <v>1.3</v>
+      </c>
+      <c r="U161">
+        <v>3.4</v>
+      </c>
+      <c r="V161">
+        <v>2.38</v>
+      </c>
+      <c r="W161">
+        <v>1.53</v>
+      </c>
+      <c r="X161">
+        <v>5.5</v>
+      </c>
+      <c r="Y161">
+        <v>1.14</v>
+      </c>
+      <c r="Z161">
+        <v>2.26</v>
+      </c>
+      <c r="AA161">
+        <v>3.9</v>
+      </c>
+      <c r="AB161">
+        <v>2.89</v>
+      </c>
+      <c r="AC161">
+        <v>1.03</v>
+      </c>
+      <c r="AD161">
+        <v>11</v>
+      </c>
+      <c r="AE161">
+        <v>1.17</v>
+      </c>
+      <c r="AF161">
+        <v>4.75</v>
+      </c>
+      <c r="AG161">
+        <v>1.52</v>
+      </c>
+      <c r="AH161">
+        <v>2.43</v>
+      </c>
+      <c r="AI161">
+        <v>1.5</v>
+      </c>
+      <c r="AJ161">
+        <v>2.5</v>
+      </c>
+      <c r="AK161">
+        <v>1.36</v>
+      </c>
+      <c r="AL161">
+        <v>1.25</v>
+      </c>
+      <c r="AM161">
+        <v>1.7</v>
+      </c>
+      <c r="AN161">
+        <v>1.75</v>
+      </c>
+      <c r="AO161">
+        <v>1.67</v>
+      </c>
+      <c r="AP161">
+        <v>1.56</v>
+      </c>
+      <c r="AQ161">
+        <v>1.8</v>
+      </c>
+      <c r="AR161">
+        <v>1.53</v>
+      </c>
+      <c r="AS161">
+        <v>1.5</v>
+      </c>
+      <c r="AT161">
+        <v>3.03</v>
+      </c>
+      <c r="AU161">
+        <v>8</v>
+      </c>
+      <c r="AV161">
+        <v>4</v>
+      </c>
+      <c r="AW161">
+        <v>16</v>
+      </c>
+      <c r="AX161">
+        <v>8</v>
+      </c>
+      <c r="AY161">
+        <v>26</v>
+      </c>
+      <c r="AZ161">
+        <v>13</v>
+      </c>
+      <c r="BA161">
+        <v>7</v>
+      </c>
+      <c r="BB161">
+        <v>4</v>
+      </c>
+      <c r="BC161">
+        <v>11</v>
+      </c>
+      <c r="BD161">
+        <v>1.81</v>
+      </c>
+      <c r="BE161">
+        <v>7</v>
+      </c>
+      <c r="BF161">
+        <v>2.15</v>
+      </c>
+      <c r="BG161">
+        <v>1.17</v>
+      </c>
+      <c r="BH161">
+        <v>4.35</v>
+      </c>
+      <c r="BI161">
+        <v>1.3</v>
+      </c>
+      <c r="BJ161">
+        <v>3.15</v>
+      </c>
+      <c r="BK161">
+        <v>1.5</v>
+      </c>
+      <c r="BL161">
+        <v>2.4</v>
+      </c>
+      <c r="BM161">
+        <v>1.78</v>
+      </c>
+      <c r="BN161">
+        <v>1.91</v>
+      </c>
+      <c r="BO161">
+        <v>2.18</v>
+      </c>
+      <c r="BP161">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7491646</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45676.39583333334</v>
+      </c>
+      <c r="F162">
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>82</v>
+      </c>
+      <c r="H162" t="s">
+        <v>74</v>
+      </c>
+      <c r="I162">
+        <v>2</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>2</v>
+      </c>
+      <c r="L162">
+        <v>2</v>
+      </c>
+      <c r="M162">
+        <v>5</v>
+      </c>
+      <c r="N162">
+        <v>7</v>
+      </c>
+      <c r="O162" t="s">
+        <v>198</v>
+      </c>
+      <c r="P162" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q162">
+        <v>2.75</v>
+      </c>
+      <c r="R162">
+        <v>2.38</v>
+      </c>
+      <c r="S162">
+        <v>3.4</v>
+      </c>
+      <c r="T162">
+        <v>1.29</v>
+      </c>
+      <c r="U162">
+        <v>3.5</v>
+      </c>
+      <c r="V162">
+        <v>2.38</v>
+      </c>
+      <c r="W162">
+        <v>1.53</v>
+      </c>
+      <c r="X162">
+        <v>5.5</v>
+      </c>
+      <c r="Y162">
+        <v>1.14</v>
+      </c>
+      <c r="Z162">
+        <v>2.13</v>
+      </c>
+      <c r="AA162">
+        <v>3.85</v>
+      </c>
+      <c r="AB162">
+        <v>3.17</v>
+      </c>
+      <c r="AC162">
+        <v>1.04</v>
+      </c>
+      <c r="AD162">
+        <v>10</v>
+      </c>
+      <c r="AE162">
+        <v>1.17</v>
+      </c>
+      <c r="AF162">
+        <v>4.75</v>
+      </c>
+      <c r="AG162">
+        <v>1.54</v>
+      </c>
+      <c r="AH162">
+        <v>2.38</v>
+      </c>
+      <c r="AI162">
+        <v>1.5</v>
+      </c>
+      <c r="AJ162">
+        <v>2.5</v>
+      </c>
+      <c r="AK162">
+        <v>1.39</v>
+      </c>
+      <c r="AL162">
+        <v>1.26</v>
+      </c>
+      <c r="AM162">
+        <v>1.63</v>
+      </c>
+      <c r="AN162">
+        <v>1.78</v>
+      </c>
+      <c r="AO162">
+        <v>2.44</v>
+      </c>
+      <c r="AP162">
+        <v>1.6</v>
+      </c>
+      <c r="AQ162">
+        <v>2.5</v>
+      </c>
+      <c r="AR162">
+        <v>1.5</v>
+      </c>
+      <c r="AS162">
+        <v>1.33</v>
+      </c>
+      <c r="AT162">
+        <v>2.83</v>
+      </c>
+      <c r="AU162">
+        <v>5</v>
+      </c>
+      <c r="AV162">
+        <v>10</v>
+      </c>
+      <c r="AW162">
+        <v>5</v>
+      </c>
+      <c r="AX162">
+        <v>10</v>
+      </c>
+      <c r="AY162">
+        <v>12</v>
+      </c>
+      <c r="AZ162">
+        <v>25</v>
+      </c>
+      <c r="BA162">
+        <v>6</v>
+      </c>
+      <c r="BB162">
+        <v>3</v>
+      </c>
+      <c r="BC162">
+        <v>9</v>
+      </c>
+      <c r="BD162">
+        <v>1.84</v>
+      </c>
+      <c r="BE162">
+        <v>6.5</v>
+      </c>
+      <c r="BF162">
+        <v>2.17</v>
+      </c>
+      <c r="BG162">
+        <v>1.21</v>
+      </c>
+      <c r="BH162">
+        <v>3.8</v>
+      </c>
+      <c r="BI162">
+        <v>1.37</v>
+      </c>
+      <c r="BJ162">
+        <v>2.8</v>
+      </c>
+      <c r="BK162">
+        <v>1.61</v>
+      </c>
+      <c r="BL162">
+        <v>2.15</v>
+      </c>
+      <c r="BM162">
+        <v>1.95</v>
+      </c>
+      <c r="BN162">
+        <v>1.74</v>
+      </c>
+      <c r="BO162">
+        <v>2.43</v>
+      </c>
+      <c r="BP162">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7491647</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45676.39583333334</v>
+      </c>
+      <c r="F163">
+        <v>18</v>
+      </c>
+      <c r="G163" t="s">
+        <v>81</v>
+      </c>
+      <c r="H163" t="s">
+        <v>71</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>2</v>
+      </c>
+      <c r="L163">
+        <v>2</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>3</v>
+      </c>
+      <c r="O163" t="s">
+        <v>199</v>
+      </c>
+      <c r="P163" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q163">
+        <v>2.88</v>
+      </c>
+      <c r="R163">
+        <v>2.4</v>
+      </c>
+      <c r="S163">
+        <v>3.25</v>
+      </c>
+      <c r="T163">
+        <v>1.29</v>
+      </c>
+      <c r="U163">
+        <v>3.5</v>
+      </c>
+      <c r="V163">
+        <v>2.25</v>
+      </c>
+      <c r="W163">
+        <v>1.57</v>
+      </c>
+      <c r="X163">
+        <v>5.5</v>
+      </c>
+      <c r="Y163">
+        <v>1.14</v>
+      </c>
+      <c r="Z163">
+        <v>2.2</v>
+      </c>
+      <c r="AA163">
+        <v>3.65</v>
+      </c>
+      <c r="AB163">
+        <v>3.16</v>
+      </c>
+      <c r="AC163">
+        <v>1.03</v>
+      </c>
+      <c r="AD163">
+        <v>11</v>
+      </c>
+      <c r="AE163">
+        <v>1.18</v>
+      </c>
+      <c r="AF163">
+        <v>4.75</v>
+      </c>
+      <c r="AG163">
+        <v>1.5</v>
+      </c>
+      <c r="AH163">
+        <v>2.48</v>
+      </c>
+      <c r="AI163">
+        <v>1.5</v>
+      </c>
+      <c r="AJ163">
+        <v>2.5</v>
+      </c>
+      <c r="AK163">
+        <v>1.4</v>
+      </c>
+      <c r="AL163">
+        <v>1.27</v>
+      </c>
+      <c r="AM163">
+        <v>1.6</v>
+      </c>
+      <c r="AN163">
+        <v>1.75</v>
+      </c>
+      <c r="AO163">
+        <v>1.67</v>
+      </c>
+      <c r="AP163">
+        <v>1.89</v>
+      </c>
+      <c r="AQ163">
+        <v>1.5</v>
+      </c>
+      <c r="AR163">
+        <v>1.52</v>
+      </c>
+      <c r="AS163">
+        <v>1.18</v>
+      </c>
+      <c r="AT163">
+        <v>2.7</v>
+      </c>
+      <c r="AU163">
+        <v>8</v>
+      </c>
+      <c r="AV163">
+        <v>5</v>
+      </c>
+      <c r="AW163">
+        <v>8</v>
+      </c>
+      <c r="AX163">
+        <v>1</v>
+      </c>
+      <c r="AY163">
+        <v>19</v>
+      </c>
+      <c r="AZ163">
+        <v>9</v>
+      </c>
+      <c r="BA163">
+        <v>9</v>
+      </c>
+      <c r="BB163">
+        <v>2</v>
+      </c>
+      <c r="BC163">
+        <v>11</v>
+      </c>
+      <c r="BD163">
+        <v>1.8</v>
+      </c>
+      <c r="BE163">
+        <v>6.75</v>
+      </c>
+      <c r="BF163">
+        <v>2.23</v>
+      </c>
+      <c r="BG163">
+        <v>1.2</v>
+      </c>
+      <c r="BH163">
+        <v>3.9</v>
+      </c>
+      <c r="BI163">
+        <v>1.36</v>
+      </c>
+      <c r="BJ163">
+        <v>2.8</v>
+      </c>
+      <c r="BK163">
+        <v>1.6</v>
+      </c>
+      <c r="BL163">
+        <v>2.17</v>
+      </c>
+      <c r="BM163">
+        <v>1.95</v>
+      </c>
+      <c r="BN163">
+        <v>1.75</v>
+      </c>
+      <c r="BO163">
+        <v>2.43</v>
+      </c>
+      <c r="BP163">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Germany 2. Bundesliga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="303">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -616,6 +616,12 @@
     <t>['36', '90+1']</t>
   </si>
   <si>
+    <t>['5']</t>
+  </si>
+  <si>
+    <t>['6', '68']</t>
+  </si>
+  <si>
     <t>['5', '35']</t>
   </si>
   <si>
@@ -865,9 +871,6 @@
     <t>['88']</t>
   </si>
   <si>
-    <t>['5']</t>
-  </si>
-  <si>
     <t>['23', '55']</t>
   </si>
   <si>
@@ -917,6 +920,9 @@
   </si>
   <si>
     <t>['40']</t>
+  </si>
+  <si>
+    <t>['28', '52', '73', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1534,7 +1540,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1740,7 +1746,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
@@ -2152,7 +2158,7 @@
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q5">
         <v>2.6</v>
@@ -2436,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ6">
         <v>1.5</v>
@@ -2564,7 +2570,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2645,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2770,7 +2776,7 @@
         <v>92</v>
       </c>
       <c r="P8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -2976,7 +2982,7 @@
         <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -3054,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ9">
         <v>1.13</v>
@@ -3182,7 +3188,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q10">
         <v>3.4</v>
@@ -3263,7 +3269,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ10">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3594,7 +3600,7 @@
         <v>97</v>
       </c>
       <c r="P12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q12">
         <v>2.65</v>
@@ -4006,7 +4012,7 @@
         <v>99</v>
       </c>
       <c r="P14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q14">
         <v>4</v>
@@ -4418,7 +4424,7 @@
         <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q16">
         <v>2.25</v>
@@ -4624,7 +4630,7 @@
         <v>101</v>
       </c>
       <c r="P17" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -4830,7 +4836,7 @@
         <v>102</v>
       </c>
       <c r="P18" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -5242,7 +5248,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -5654,7 +5660,7 @@
         <v>92</v>
       </c>
       <c r="P22" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q22">
         <v>3.1</v>
@@ -5735,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR22">
         <v>1.26</v>
@@ -5860,7 +5866,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -5938,7 +5944,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ23">
         <v>1.56</v>
@@ -6353,7 +6359,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ25">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR25">
         <v>2.21</v>
@@ -6478,7 +6484,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q26">
         <v>4.33</v>
@@ -6684,7 +6690,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6890,7 +6896,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q28">
         <v>2.88</v>
@@ -6968,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ28">
         <v>1.3</v>
@@ -7302,7 +7308,7 @@
         <v>92</v>
       </c>
       <c r="P30" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q30">
         <v>3.5</v>
@@ -7508,7 +7514,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q31">
         <v>1.84</v>
@@ -7920,7 +7926,7 @@
         <v>92</v>
       </c>
       <c r="P33" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -8126,7 +8132,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q34">
         <v>2.75</v>
@@ -8538,7 +8544,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -8744,7 +8750,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q37">
         <v>3.91</v>
@@ -8950,7 +8956,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q38">
         <v>3.5</v>
@@ -9362,7 +9368,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -9443,7 +9449,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ40">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR40">
         <v>1.31</v>
@@ -9568,7 +9574,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -9774,7 +9780,7 @@
         <v>120</v>
       </c>
       <c r="P42" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -9855,7 +9861,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ42">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR42">
         <v>1.72</v>
@@ -9980,7 +9986,7 @@
         <v>104</v>
       </c>
       <c r="P43" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q43">
         <v>1.95</v>
@@ -10264,7 +10270,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ44">
         <v>1.5</v>
@@ -10392,7 +10398,7 @@
         <v>92</v>
       </c>
       <c r="P45" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -10804,7 +10810,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q47">
         <v>2.64</v>
@@ -11010,7 +11016,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q48">
         <v>2.2</v>
@@ -11216,7 +11222,7 @@
         <v>124</v>
       </c>
       <c r="P49" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q49">
         <v>3.5</v>
@@ -11422,7 +11428,7 @@
         <v>92</v>
       </c>
       <c r="P50" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q50">
         <v>3.4</v>
@@ -11834,7 +11840,7 @@
         <v>126</v>
       </c>
       <c r="P52" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q52">
         <v>3.25</v>
@@ -12040,7 +12046,7 @@
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -12246,7 +12252,7 @@
         <v>128</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q54">
         <v>3.2</v>
@@ -12324,7 +12330,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ54">
         <v>1.5</v>
@@ -12452,7 +12458,7 @@
         <v>92</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q55">
         <v>3</v>
@@ -12658,7 +12664,7 @@
         <v>129</v>
       </c>
       <c r="P56" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q56">
         <v>3.07</v>
@@ -12739,7 +12745,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ56">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR56">
         <v>1.5</v>
@@ -12864,7 +12870,7 @@
         <v>130</v>
       </c>
       <c r="P57" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q57">
         <v>3.4</v>
@@ -12942,7 +12948,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ57">
         <v>2.13</v>
@@ -13070,7 +13076,7 @@
         <v>131</v>
       </c>
       <c r="P58" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13357,7 +13363,7 @@
         <v>1</v>
       </c>
       <c r="AQ59">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR59">
         <v>1.4</v>
@@ -13482,7 +13488,7 @@
         <v>100</v>
       </c>
       <c r="P60" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q60">
         <v>2.65</v>
@@ -13688,7 +13694,7 @@
         <v>132</v>
       </c>
       <c r="P61" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q61">
         <v>3.2</v>
@@ -14100,7 +14106,7 @@
         <v>134</v>
       </c>
       <c r="P63" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -14306,7 +14312,7 @@
         <v>135</v>
       </c>
       <c r="P64" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q64">
         <v>2.1</v>
@@ -14718,7 +14724,7 @@
         <v>137</v>
       </c>
       <c r="P66" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q66">
         <v>2.2</v>
@@ -15211,7 +15217,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ68">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR68">
         <v>1.33</v>
@@ -15336,7 +15342,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15542,7 +15548,7 @@
         <v>140</v>
       </c>
       <c r="P70" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q70">
         <v>2.75</v>
@@ -15748,7 +15754,7 @@
         <v>141</v>
       </c>
       <c r="P71" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15826,7 +15832,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -16160,7 +16166,7 @@
         <v>92</v>
       </c>
       <c r="P73" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16653,7 +16659,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ75">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR75">
         <v>1.4</v>
@@ -16778,7 +16784,7 @@
         <v>145</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16984,7 +16990,7 @@
         <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q77">
         <v>4.5</v>
@@ -17808,7 +17814,7 @@
         <v>92</v>
       </c>
       <c r="P81" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q81">
         <v>2.38</v>
@@ -17886,7 +17892,7 @@
         <v>1</v>
       </c>
       <c r="AP81">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ81">
         <v>0.89</v>
@@ -18014,7 +18020,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18220,7 +18226,7 @@
         <v>114</v>
       </c>
       <c r="P83" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q83">
         <v>2.15</v>
@@ -18426,7 +18432,7 @@
         <v>149</v>
       </c>
       <c r="P84" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18632,7 +18638,7 @@
         <v>150</v>
       </c>
       <c r="P85" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q85">
         <v>2.54</v>
@@ -18838,7 +18844,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -19044,7 +19050,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q87">
         <v>3.6</v>
@@ -19250,7 +19256,7 @@
         <v>153</v>
       </c>
       <c r="P88" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q88">
         <v>2.25</v>
@@ -19331,7 +19337,7 @@
         <v>1</v>
       </c>
       <c r="AQ88">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR88">
         <v>1.59</v>
@@ -19456,7 +19462,7 @@
         <v>154</v>
       </c>
       <c r="P89" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q89">
         <v>2.3</v>
@@ -19662,7 +19668,7 @@
         <v>92</v>
       </c>
       <c r="P90" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q90">
         <v>3</v>
@@ -19740,7 +19746,7 @@
         <v>0.25</v>
       </c>
       <c r="AP90">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ90">
         <v>0.89</v>
@@ -20692,7 +20698,7 @@
         <v>157</v>
       </c>
       <c r="P95" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -20770,7 +20776,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ95">
         <v>1.33</v>
@@ -21104,7 +21110,7 @@
         <v>92</v>
       </c>
       <c r="P97" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21310,7 +21316,7 @@
         <v>159</v>
       </c>
       <c r="P98" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q98">
         <v>2.7</v>
@@ -21597,7 +21603,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ99">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR99">
         <v>1.63</v>
@@ -21722,7 +21728,7 @@
         <v>155</v>
       </c>
       <c r="P100" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q100">
         <v>1.95</v>
@@ -21928,7 +21934,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q101">
         <v>3.7</v>
@@ -22215,7 +22221,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ102">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR102">
         <v>1.42</v>
@@ -22546,7 +22552,7 @@
         <v>162</v>
       </c>
       <c r="P104" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q104">
         <v>2.7</v>
@@ -22830,7 +22836,7 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ105">
         <v>0.8</v>
@@ -22958,7 +22964,7 @@
         <v>163</v>
       </c>
       <c r="P106" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q106">
         <v>2.62</v>
@@ -23164,7 +23170,7 @@
         <v>164</v>
       </c>
       <c r="P107" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q107">
         <v>2.1</v>
@@ -23576,7 +23582,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -23782,7 +23788,7 @@
         <v>167</v>
       </c>
       <c r="P110" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24194,7 +24200,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q112">
         <v>3.1</v>
@@ -24272,7 +24278,7 @@
         <v>1.5</v>
       </c>
       <c r="AP112">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ112">
         <v>1.5</v>
@@ -24400,7 +24406,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24606,7 +24612,7 @@
         <v>92</v>
       </c>
       <c r="P114" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q114">
         <v>2.6</v>
@@ -24812,7 +24818,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q115">
         <v>2.5</v>
@@ -25018,7 +25024,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q116">
         <v>2.2</v>
@@ -25224,7 +25230,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q117">
         <v>2.63</v>
@@ -25305,7 +25311,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ117">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR117">
         <v>1.79</v>
@@ -25430,7 +25436,7 @@
         <v>92</v>
       </c>
       <c r="P118" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25636,7 +25642,7 @@
         <v>95</v>
       </c>
       <c r="P119" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -25714,7 +25720,7 @@
         <v>1.83</v>
       </c>
       <c r="AP119">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ119">
         <v>1.8</v>
@@ -25842,7 +25848,7 @@
         <v>92</v>
       </c>
       <c r="P120" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
@@ -25923,7 +25929,7 @@
         <v>1</v>
       </c>
       <c r="AQ120">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -26048,7 +26054,7 @@
         <v>173</v>
       </c>
       <c r="P121" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q121">
         <v>2.35</v>
@@ -26254,7 +26260,7 @@
         <v>174</v>
       </c>
       <c r="P122" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q122">
         <v>2.85</v>
@@ -26872,7 +26878,7 @@
         <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27078,7 +27084,7 @@
         <v>176</v>
       </c>
       <c r="P126" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q126">
         <v>3.25</v>
@@ -27696,7 +27702,7 @@
         <v>179</v>
       </c>
       <c r="P129" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q129">
         <v>2.3</v>
@@ -27902,7 +27908,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q130">
         <v>2.9</v>
@@ -28108,7 +28114,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="Q131">
         <v>3.3</v>
@@ -28186,7 +28192,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ131">
         <v>1.8</v>
@@ -28314,7 +28320,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q132">
         <v>2.15</v>
@@ -28520,7 +28526,7 @@
         <v>183</v>
       </c>
       <c r="P133" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q133">
         <v>3</v>
@@ -28726,7 +28732,7 @@
         <v>184</v>
       </c>
       <c r="P134" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
@@ -29013,7 +29019,7 @@
         <v>1</v>
       </c>
       <c r="AQ135">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR135">
         <v>1.54</v>
@@ -29138,7 +29144,7 @@
         <v>92</v>
       </c>
       <c r="P136" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q136">
         <v>6</v>
@@ -29344,7 +29350,7 @@
         <v>186</v>
       </c>
       <c r="P137" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q137">
         <v>1.87</v>
@@ -29550,7 +29556,7 @@
         <v>120</v>
       </c>
       <c r="P138" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q138">
         <v>2.1</v>
@@ -29962,7 +29968,7 @@
         <v>187</v>
       </c>
       <c r="P140" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q140">
         <v>3.1</v>
@@ -30040,7 +30046,7 @@
         <v>1.63</v>
       </c>
       <c r="AP140">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ140">
         <v>1.56</v>
@@ -30374,7 +30380,7 @@
         <v>188</v>
       </c>
       <c r="P142" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q142">
         <v>2.38</v>
@@ -30455,7 +30461,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ142">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AR142">
         <v>1.45</v>
@@ -30864,7 +30870,7 @@
         <v>0.71</v>
       </c>
       <c r="AP144">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ144">
         <v>0.89</v>
@@ -30992,7 +30998,7 @@
         <v>92</v>
       </c>
       <c r="P145" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q145">
         <v>3.4</v>
@@ -31198,7 +31204,7 @@
         <v>191</v>
       </c>
       <c r="P146" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31404,7 +31410,7 @@
         <v>192</v>
       </c>
       <c r="P147" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q147">
         <v>2.5</v>
@@ -32022,7 +32028,7 @@
         <v>130</v>
       </c>
       <c r="P150" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q150">
         <v>2.6</v>
@@ -32309,7 +32315,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ151">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR151">
         <v>1.49</v>
@@ -32434,7 +32440,7 @@
         <v>194</v>
       </c>
       <c r="P152" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q152">
         <v>4.5</v>
@@ -32846,7 +32852,7 @@
         <v>92</v>
       </c>
       <c r="P154" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q154">
         <v>4</v>
@@ -33052,7 +33058,7 @@
         <v>195</v>
       </c>
       <c r="P155" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q155">
         <v>2.88</v>
@@ -33258,7 +33264,7 @@
         <v>92</v>
       </c>
       <c r="P156" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q156">
         <v>4.5</v>
@@ -34288,7 +34294,7 @@
         <v>161</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q161">
         <v>2.75</v>
@@ -34494,7 +34500,7 @@
         <v>198</v>
       </c>
       <c r="P162" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q162">
         <v>2.75</v>
@@ -34700,7 +34706,7 @@
         <v>199</v>
       </c>
       <c r="P163" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q163">
         <v>2.88</v>
@@ -34857,6 +34863,418 @@
       </c>
       <c r="BP163">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7491659</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45681.60416666666</v>
+      </c>
+      <c r="F164">
+        <v>19</v>
+      </c>
+      <c r="G164" t="s">
+        <v>74</v>
+      </c>
+      <c r="H164" t="s">
+        <v>86</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>2</v>
+      </c>
+      <c r="O164" t="s">
+        <v>200</v>
+      </c>
+      <c r="P164" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q164">
+        <v>2.15</v>
+      </c>
+      <c r="R164">
+        <v>2.3</v>
+      </c>
+      <c r="S164">
+        <v>4.5</v>
+      </c>
+      <c r="T164">
+        <v>1.29</v>
+      </c>
+      <c r="U164">
+        <v>3.25</v>
+      </c>
+      <c r="V164">
+        <v>2.3</v>
+      </c>
+      <c r="W164">
+        <v>1.53</v>
+      </c>
+      <c r="X164">
+        <v>5.25</v>
+      </c>
+      <c r="Y164">
+        <v>1.13</v>
+      </c>
+      <c r="Z164">
+        <v>1.81</v>
+      </c>
+      <c r="AA164">
+        <v>4</v>
+      </c>
+      <c r="AB164">
+        <v>4.33</v>
+      </c>
+      <c r="AC164">
+        <v>1.04</v>
+      </c>
+      <c r="AD164">
+        <v>10</v>
+      </c>
+      <c r="AE164">
+        <v>1.18</v>
+      </c>
+      <c r="AF164">
+        <v>4.5</v>
+      </c>
+      <c r="AG164">
+        <v>1.57</v>
+      </c>
+      <c r="AH164">
+        <v>2.25</v>
+      </c>
+      <c r="AI164">
+        <v>1.63</v>
+      </c>
+      <c r="AJ164">
+        <v>2.1</v>
+      </c>
+      <c r="AK164">
+        <v>1.19</v>
+      </c>
+      <c r="AL164">
+        <v>1.23</v>
+      </c>
+      <c r="AM164">
+        <v>2.15</v>
+      </c>
+      <c r="AN164">
+        <v>0.75</v>
+      </c>
+      <c r="AO164">
+        <v>0.22</v>
+      </c>
+      <c r="AP164">
+        <v>0.78</v>
+      </c>
+      <c r="AQ164">
+        <v>0.3</v>
+      </c>
+      <c r="AR164">
+        <v>1.62</v>
+      </c>
+      <c r="AS164">
+        <v>1.12</v>
+      </c>
+      <c r="AT164">
+        <v>2.74</v>
+      </c>
+      <c r="AU164">
+        <v>6</v>
+      </c>
+      <c r="AV164">
+        <v>3</v>
+      </c>
+      <c r="AW164">
+        <v>12</v>
+      </c>
+      <c r="AX164">
+        <v>5</v>
+      </c>
+      <c r="AY164">
+        <v>22</v>
+      </c>
+      <c r="AZ164">
+        <v>8</v>
+      </c>
+      <c r="BA164">
+        <v>10</v>
+      </c>
+      <c r="BB164">
+        <v>6</v>
+      </c>
+      <c r="BC164">
+        <v>16</v>
+      </c>
+      <c r="BD164">
+        <v>1.5</v>
+      </c>
+      <c r="BE164">
+        <v>6.5</v>
+      </c>
+      <c r="BF164">
+        <v>2.8</v>
+      </c>
+      <c r="BG164">
+        <v>1.35</v>
+      </c>
+      <c r="BH164">
+        <v>2.9</v>
+      </c>
+      <c r="BI164">
+        <v>1.6</v>
+      </c>
+      <c r="BJ164">
+        <v>2.17</v>
+      </c>
+      <c r="BK164">
+        <v>1.98</v>
+      </c>
+      <c r="BL164">
+        <v>1.72</v>
+      </c>
+      <c r="BM164">
+        <v>2.55</v>
+      </c>
+      <c r="BN164">
+        <v>1.44</v>
+      </c>
+      <c r="BO164">
+        <v>3.3</v>
+      </c>
+      <c r="BP164">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7491656</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45681.60416666666</v>
+      </c>
+      <c r="F165">
+        <v>19</v>
+      </c>
+      <c r="G165" t="s">
+        <v>77</v>
+      </c>
+      <c r="H165" t="s">
+        <v>80</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+      <c r="J165">
+        <v>1</v>
+      </c>
+      <c r="K165">
+        <v>2</v>
+      </c>
+      <c r="L165">
+        <v>2</v>
+      </c>
+      <c r="M165">
+        <v>4</v>
+      </c>
+      <c r="N165">
+        <v>6</v>
+      </c>
+      <c r="O165" t="s">
+        <v>201</v>
+      </c>
+      <c r="P165" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q165">
+        <v>2.85</v>
+      </c>
+      <c r="R165">
+        <v>2.3</v>
+      </c>
+      <c r="S165">
+        <v>3.1</v>
+      </c>
+      <c r="T165">
+        <v>1.28</v>
+      </c>
+      <c r="U165">
+        <v>3.4</v>
+      </c>
+      <c r="V165">
+        <v>2.29</v>
+      </c>
+      <c r="W165">
+        <v>1.56</v>
+      </c>
+      <c r="X165">
+        <v>4.95</v>
+      </c>
+      <c r="Y165">
+        <v>1.14</v>
+      </c>
+      <c r="Z165">
+        <v>2.42</v>
+      </c>
+      <c r="AA165">
+        <v>3.7</v>
+      </c>
+      <c r="AB165">
+        <v>2.84</v>
+      </c>
+      <c r="AC165">
+        <v>1.04</v>
+      </c>
+      <c r="AD165">
+        <v>10</v>
+      </c>
+      <c r="AE165">
+        <v>1.18</v>
+      </c>
+      <c r="AF165">
+        <v>4.75</v>
+      </c>
+      <c r="AG165">
+        <v>1.57</v>
+      </c>
+      <c r="AH165">
+        <v>2.25</v>
+      </c>
+      <c r="AI165">
+        <v>1.47</v>
+      </c>
+      <c r="AJ165">
+        <v>2.6</v>
+      </c>
+      <c r="AK165">
+        <v>1.45</v>
+      </c>
+      <c r="AL165">
+        <v>1.22</v>
+      </c>
+      <c r="AM165">
+        <v>1.55</v>
+      </c>
+      <c r="AN165">
+        <v>1.22</v>
+      </c>
+      <c r="AO165">
+        <v>1.56</v>
+      </c>
+      <c r="AP165">
+        <v>1.1</v>
+      </c>
+      <c r="AQ165">
+        <v>1.7</v>
+      </c>
+      <c r="AR165">
+        <v>1.4</v>
+      </c>
+      <c r="AS165">
+        <v>1.37</v>
+      </c>
+      <c r="AT165">
+        <v>2.77</v>
+      </c>
+      <c r="AU165">
+        <v>5</v>
+      </c>
+      <c r="AV165">
+        <v>8</v>
+      </c>
+      <c r="AW165">
+        <v>7</v>
+      </c>
+      <c r="AX165">
+        <v>7</v>
+      </c>
+      <c r="AY165">
+        <v>14</v>
+      </c>
+      <c r="AZ165">
+        <v>19</v>
+      </c>
+      <c r="BA165">
+        <v>2</v>
+      </c>
+      <c r="BB165">
+        <v>4</v>
+      </c>
+      <c r="BC165">
+        <v>6</v>
+      </c>
+      <c r="BD165">
+        <v>1.92</v>
+      </c>
+      <c r="BE165">
+        <v>6.4</v>
+      </c>
+      <c r="BF165">
+        <v>2.08</v>
+      </c>
+      <c r="BG165">
+        <v>1.3</v>
+      </c>
+      <c r="BH165">
+        <v>3.05</v>
+      </c>
+      <c r="BI165">
+        <v>1.54</v>
+      </c>
+      <c r="BJ165">
+        <v>2.3</v>
+      </c>
+      <c r="BK165">
+        <v>1.88</v>
+      </c>
+      <c r="BL165">
+        <v>1.81</v>
+      </c>
+      <c r="BM165">
+        <v>2.33</v>
+      </c>
+      <c r="BN165">
+        <v>1.5</v>
+      </c>
+      <c r="BO165">
+        <v>3.05</v>
+      </c>
+      <c r="BP165">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>
